--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127804512</v>
+        <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>92097</v>
+        <v>79996</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624255</v>
+        <v>624385</v>
       </c>
       <c r="R3" t="n">
-        <v>6853188</v>
+        <v>6853379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127804095</v>
+        <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>79996</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,26 +889,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>392</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -916,13 +917,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624385</v>
+        <v>624037</v>
       </c>
       <c r="R4" t="n">
-        <v>6853379</v>
+        <v>6853147</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127804289</v>
+        <v>127805341</v>
       </c>
       <c r="B5" t="n">
-        <v>91610</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,13 +1018,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624255</v>
+        <v>624083</v>
       </c>
       <c r="R5" t="n">
-        <v>6853188</v>
+        <v>6853162</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,38 +1081,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127805309</v>
+        <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>92103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624037</v>
+        <v>624283</v>
       </c>
       <c r="R6" t="n">
-        <v>6853147</v>
+        <v>6853189</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1182,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127805341</v>
+        <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>91322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624083</v>
+        <v>624265</v>
       </c>
       <c r="R7" t="n">
-        <v>6853162</v>
+        <v>6853335</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,6 +1280,433 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127880991</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91338</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>624038</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6853151</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127882505</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>624166</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6853271</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127804289</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91616</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Flavidoporia pulvinascens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>624255</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6853188</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128048266</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91536</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1347</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asptagging</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Radulodon erikssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ryvarden</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>624247</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6853194</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>79996</v>
+        <v>79999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127805341</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91322</v>
+        <v>91325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127882505</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>79999</v>
+        <v>80005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127805341</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91325</v>
+        <v>91333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127882505</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>91627</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91539</v>
+        <v>91547</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91333</v>
+        <v>91334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91627</v>
+        <v>91628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91547</v>
+        <v>91548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80005</v>
+        <v>80008</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127805341</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91336</v>
+        <v>91344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127882505</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91630</v>
+        <v>91638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>91558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127805282</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80008</v>
+        <v>80061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>127805309</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>127805341</v>
       </c>
       <c r="B5" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91344</v>
+        <v>91436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127882505</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91638</v>
+        <v>91730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91558</v>
+        <v>91650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1708,6 +1708,339 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128619291</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>624359</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6853253</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128619219</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>624296</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6853243</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Knappt 100 plantor.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128619158</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623959</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6853127</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 70 plantor. Ett par blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1084,7 +1084,7 @@
         <v>127883190</v>
       </c>
       <c r="B6" t="n">
-        <v>92217</v>
+        <v>92229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>127881871</v>
       </c>
       <c r="B7" t="n">
-        <v>91436</v>
+        <v>91448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>127880991</v>
       </c>
       <c r="B8" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>127882505</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>127804289</v>
       </c>
       <c r="B10" t="n">
-        <v>91730</v>
+        <v>91746</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         <v>128048266</v>
       </c>
       <c r="B11" t="n">
-        <v>91650</v>
+        <v>91662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,6 +2041,107 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128715868</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>624408</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6853257</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -1713,7 +1713,7 @@
         <v>128619291</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>128619219</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>128619158</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>128715868</v>
       </c>
       <c r="B15" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2142,6 +2142,107 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129430851</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3382</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Aspskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Conferticium ravum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>624267</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6853196</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92748</v>
+        <v>92752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92752</v>
+        <v>92753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92753</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92796</v>
+        <v>92800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2147,7 +2147,7 @@
         <v>129430851</v>
       </c>
       <c r="B16" t="n">
-        <v>92800</v>
+        <v>92802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80223</v>
+        <v>80224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80224</v>
+        <v>80226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80226</v>
+        <v>80227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127804095</v>
       </c>
       <c r="B3" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2243,6 +2243,127 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131698269</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92301</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1208</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aspvaxskinn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phlebia bresadolae</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Parmasto</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>624257</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6853195</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Grov asplåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Populus tremula # Grov asplåga</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92301</v>
+        <v>92302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92302</v>
+        <v>92303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92303</v>
+        <v>92306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92306</v>
+        <v>92312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92312</v>
+        <v>92315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92315</v>
+        <v>92320</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -2248,7 +2248,7 @@
         <v>131698269</v>
       </c>
       <c r="B17" t="n">
-        <v>92320</v>
+        <v>92322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2243,127 +2243,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>131698269</v>
-      </c>
-      <c r="B17" t="n">
-        <v>92363</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DD</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1208</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Aspvaxskinn</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phlebia bresadolae</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Parmasto</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gulsjön, Hls</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>624257</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6853195</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Rogsta</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Grov asplåga</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Populus tremula # Grov asplåga</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Maria Wallin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37576-2025 artfynd.xlsx
+++ b/artfynd/A 37576-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127805282</v>
+        <v>127804289</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623986</v>
+        <v>624255</v>
       </c>
       <c r="R2" t="n">
-        <v>6853147</v>
+        <v>6853188</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +762,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Maria Wallin</t>
@@ -777,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127804095</v>
+        <v>127883190</v>
       </c>
       <c r="B3" t="n">
-        <v>80228</v>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624385</v>
+        <v>624283</v>
       </c>
       <c r="R3" t="n">
-        <v>6853379</v>
+        <v>6853189</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127805309</v>
+        <v>127804095</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,27 +898,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -917,13 +925,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624037</v>
+        <v>624385</v>
       </c>
       <c r="R4" t="n">
-        <v>6853147</v>
+        <v>6853379</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127805341</v>
+        <v>128486978</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,21 +999,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1106</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624083</v>
+        <v>624276</v>
       </c>
       <c r="R5" t="n">
-        <v>6853162</v>
+        <v>6853183</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1048,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127883190</v>
+        <v>127880991</v>
       </c>
       <c r="B6" t="n">
-        <v>92229</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624283</v>
+        <v>624038</v>
       </c>
       <c r="R6" t="n">
-        <v>6853189</v>
+        <v>6853151</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1182,32 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127881871</v>
+        <v>128048266</v>
       </c>
       <c r="B7" t="n">
-        <v>91448</v>
+        <v>92120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>1347</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Asptagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Radulodon erikssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Ryvarden</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,13 +1228,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624265</v>
+        <v>624247</v>
       </c>
       <c r="R7" t="n">
-        <v>6853335</v>
+        <v>6853194</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1264,11 +1272,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW7" t="inlineStr">
         <is>
           <t>Maria Wallin</t>
@@ -1283,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127880991</v>
+        <v>129430851</v>
       </c>
       <c r="B8" t="n">
-        <v>91464</v>
+        <v>93117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,21 +1315,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3382</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Conferticium ravum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1321,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624038</v>
+        <v>624267</v>
       </c>
       <c r="R8" t="n">
-        <v>6853151</v>
+        <v>6853196</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1351,12 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127882505</v>
+        <v>128715868</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1395,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1422,13 +1443,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>624166</v>
+        <v>624408</v>
       </c>
       <c r="R9" t="n">
-        <v>6853271</v>
+        <v>6853257</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,12 +1473,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,32 +1506,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127804289</v>
+        <v>127881871</v>
       </c>
       <c r="B10" t="n">
-        <v>91746</v>
+        <v>91893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>4660</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1523,13 +1544,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>624255</v>
+        <v>624265</v>
       </c>
       <c r="R10" t="n">
-        <v>6853188</v>
+        <v>6853335</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1572,16 +1593,6 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Mattias Edman</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
       <c r="AW10" t="inlineStr">
         <is>
           <t>Maria Wallin</t>
@@ -1596,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128048266</v>
+        <v>127882505</v>
       </c>
       <c r="B11" t="n">
-        <v>91662</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1347</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asptagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Radulodon erikssonii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Ryvarden</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1645,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>624247</v>
+        <v>624166</v>
       </c>
       <c r="R11" t="n">
-        <v>6853194</v>
+        <v>6853271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,24 +1689,11 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Mattias Edman</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
           <t>Maria Wallin</t>
@@ -1710,56 +1708,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128619291</v>
+        <v>2083649</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gulsjön, Hls</t>
+          <t>GULSJÖN (16H0g01), Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>624359</v>
+        <v>624278</v>
       </c>
       <c r="R12" t="n">
-        <v>6853253</v>
+        <v>6853202</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,17 +1773,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>1994-08-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>1994-08-15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 50 plantor.</t>
+          <t>160706011 / LEP SATU / Enstaka-sparsam (1)  / OBJ.AREA:1,2 ha</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,61 +1792,59 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Jan-olov Edlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128619219</v>
+        <v>127805341</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1864,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>624296</v>
+        <v>624083</v>
       </c>
       <c r="R13" t="n">
-        <v>6853243</v>
+        <v>6853162</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,17 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Knappt 100 plantor.</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,17 +1908,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128619158</v>
+        <v>127805282</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,11 +1943,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1975,13 +1954,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623959</v>
+        <v>623986</v>
       </c>
       <c r="R14" t="n">
-        <v>6853127</v>
+        <v>6853147</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2005,17 +1984,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ca 70 plantor. Ett par blomstänglar.</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,44 +2010,45 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janne Larsson</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128715868</v>
+        <v>127805309</v>
       </c>
       <c r="B15" t="n">
-        <v>92847</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2081,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>624408</v>
+        <v>624037</v>
       </c>
       <c r="R15" t="n">
-        <v>6853257</v>
+        <v>6853147</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2111,12 +2086,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,37 +2119,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129430851</v>
+        <v>128619158</v>
       </c>
       <c r="B16" t="n">
-        <v>92802</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3382</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aspskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Conferticium ravum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Burt) Ginns &amp; G.W. Freeman</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2182,13 +2162,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>624267</v>
+        <v>623959</v>
       </c>
       <c r="R16" t="n">
-        <v>6853196</v>
+        <v>6853127</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2218,6 +2198,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 70 plantor. Ett par blomstänglar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,10 +2223,232 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Janne Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128619219</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>624296</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6853243</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Knappt 100 plantor.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128619291</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gulsjön, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>624359</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6853253</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rogsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maria Wallin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Janne Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
